--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484263_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484263_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1097</v>
+        <v>3.9436</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4932</v>
+        <v>2.8808</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6165</v>
+        <v>1.0629</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3957</v>
+        <v>1.8629</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0954</v>
+        <v>0.2443</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6998</v>
+        <v>1.6186</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1742</v>
+        <v>3.5903</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6823</v>
+        <v>2.3753</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.5081</v>
+        <v>1.215</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7785</v>
+        <v>-1.7273</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5868</v>
+        <v>-2.131</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8083</v>
+        <v>0.4037</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.3674</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.3208</v>
+        <v>-4.2975</v>
       </c>
       <c r="R2" t="n">
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2927</v>
+        <v>0.5812</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9839</v>
+        <v>0.5415</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6912</v>
+        <v>0.0398</v>
       </c>
       <c r="V2" t="n">
-        <v>3.7887</v>
+        <v>3.8436</v>
       </c>
       <c r="W2" t="n">
-        <v>3.6559</v>
+        <v>3.0466</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1328</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9225</v>
+        <v>3.8515</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7177</v>
+        <v>2.7448</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7952</v>
+        <v>1.1068</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.1617</v>
+        <v>0.3957</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1059</v>
+        <v>1.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2677</v>
+        <v>-0.6998</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2632</v>
+        <v>1.1742</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0041</v>
+        <v>2.6823</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2673</v>
+        <v>-1.5081</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8986</v>
+        <v>-0.7785</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8982</v>
+        <v>-1.5868</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0004</v>
+        <v>0.8083</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3907</v>
+        <v>-3.3208</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3111</v>
+        <v>1.0345</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5519</v>
+        <v>1.2355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7592</v>
+        <v>-0.201</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3824</v>
+        <v>3.7887</v>
       </c>
       <c r="W3" t="n">
-        <v>4.8197</v>
+        <v>3.6559</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4373</v>
+        <v>0.1328</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3174</v>
+        <v>2.8412</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4452</v>
+        <v>4.9088</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8722</v>
+        <v>-2.0676</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8629</v>
+        <v>-1.1617</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2443</v>
+        <v>0.1059</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6186</v>
+        <v>-1.2677</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5903</v>
+        <v>-0.2632</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3753</v>
+        <v>1.0041</v>
       </c>
       <c r="L4" t="n">
-        <v>1.215</v>
+        <v>-1.2673</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7273</v>
+        <v>-0.8986</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.131</v>
+        <v>-0.8982</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4037</v>
+        <v>-0.0004</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.3441</v>
+        <v>0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.2975</v>
+        <v>-0.3907</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.045</v>
+        <v>1.2299</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8941</v>
+        <v>0.743</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1509</v>
+        <v>0.4869</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8436</v>
+        <v>2.3824</v>
       </c>
       <c r="W4" t="n">
-        <v>3.0466</v>
+        <v>4.8197</v>
       </c>
       <c r="X4" t="n">
-        <v>0.797</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2003</v>
+        <v>2.2959</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2609</v>
+        <v>2.2203</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0606</v>
+        <v>0.0755</v>
       </c>
       <c r="G5" t="n">
         <v>1.0719</v>
@@ -844,13 +844,13 @@
         <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5695</v>
+        <v>0.6651</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8173</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2477</v>
+        <v>-0.1116</v>
       </c>
       <c r="V5" t="n">
         <v>-0.8086</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9622</v>
+        <v>2.0072</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5248</v>
+        <v>0.3646</v>
       </c>
       <c r="F6" t="n">
-        <v>2.487</v>
+        <v>1.6427</v>
       </c>
       <c r="G6" t="n">
         <v>1.2935</v>
@@ -922,13 +922,13 @@
         <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8484</v>
+        <v>0.8934</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5226</v>
+        <v>0.3668</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3709</v>
+        <v>0.5266</v>
       </c>
       <c r="V6" t="n">
         <v>0.797</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3467</v>
+        <v>0.4706</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6015</v>
+        <v>-0.9749</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2548</v>
+        <v>1.4455</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5006</v>
@@ -1000,13 +1000,13 @@
         <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.58</v>
+        <v>0.2373</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.22</v>
+        <v>0.4067</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.36</v>
+        <v>-0.1694</v>
       </c>
       <c r="V7" t="n">
         <v>1.9059</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4227</v>
+        <v>-0.6389</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7255</v>
+        <v>-0.8045</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3028</v>
+        <v>0.1656</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.1952</v>
+        <v>-1.4752</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.197</v>
+        <v>-0.9762</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9982</v>
+        <v>-0.499</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.2266</v>
+        <v>-0.7117</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6335</v>
+        <v>-0.0781</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9686</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5636</v>
+        <v>-0.8982</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4051</v>
+        <v>0.1346</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1865</v>
+        <v>0.3323</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9467</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2398</v>
+        <v>0.425</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6093</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.036</v>
+        <v>-0.889</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2288</v>
+        <v>-1.11</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1928</v>
+        <v>0.221</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4752</v>
+        <v>-3.1952</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9762</v>
+        <v>-2.197</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.499</v>
+        <v>-0.9982</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7117</v>
+        <v>-2.2266</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0781</v>
+        <v>-1.6335</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.9686</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8982</v>
+        <v>-0.5636</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1346</v>
+        <v>-0.4051</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0649</v>
+        <v>0.7202</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5172</v>
+        <v>0.5621</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4523</v>
+        <v>0.1581</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1272</v>
+        <v>-1.1466</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4324</v>
+        <v>-1.5335</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3053</v>
+        <v>0.387</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0024</v>
@@ -1234,13 +1234,13 @@
         <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8166</v>
+        <v>0.7972</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8035</v>
+        <v>0.7024</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0131</v>
+        <v>0.0949</v>
       </c>
       <c r="V10" t="n">
         <v>0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.314</v>
+        <v>-2.5623</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.394</v>
+        <v>-2.7785</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08</v>
+        <v>0.2162</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4489</v>
@@ -1312,13 +1312,13 @@
         <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1034</v>
+        <v>0.855</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1282</v>
+        <v>0.7437</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0248</v>
+        <v>0.1113</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5545</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.265499999999999</v>
+        <v>10.1732</v>
       </c>
       <c r="E12" t="n">
-        <v>5.009999999999998</v>
+        <v>5.9179</v>
       </c>
       <c r="F12" t="n">
-        <v>4.2556</v>
+        <v>4.255599999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-8.16</v>
@@ -1366,7 +1366,7 @@
         <v>-0.7978000000000005</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2173</v>
+        <v>1.217300000000001</v>
       </c>
       <c r="L12" t="n">
         <v>-2.0154</v>
@@ -1390,13 +1390,13 @@
         <v>12.6973</v>
       </c>
       <c r="S12" t="n">
-        <v>6.4383</v>
+        <v>7.3461</v>
       </c>
       <c r="T12" t="n">
-        <v>5.0776</v>
+        <v>5.9856</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3607</v>
+        <v>1.3606</v>
       </c>
       <c r="V12" t="n">
         <v>11.9638</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9172</v>
+        <v>2.286</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1783</v>
+        <v>1.1672</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7389</v>
+        <v>1.1188</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7645999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>1.9534</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8321</v>
+        <v>0.2009</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3649</v>
+        <v>0.3537</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.1529</v>
       </c>
       <c r="V13" t="n">
         <v>1.873</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6416</v>
+        <v>1.9086</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6466</v>
+        <v>2.0511</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0049</v>
+        <v>-0.1425</v>
       </c>
       <c r="G14" t="n">
         <v>4.5658</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4733</v>
+        <v>-0.2064</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4015</v>
+        <v>0.0029</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0718</v>
+        <v>-0.2093</v>
       </c>
       <c r="V14" t="n">
         <v>-2.0601</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3124</v>
+        <v>1.0682</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7635</v>
+        <v>1.168</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4511</v>
+        <v>-0.0997</v>
       </c>
       <c r="G15" t="n">
         <v>2.0932</v>
@@ -1624,13 +1624,13 @@
         <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3267</v>
+        <v>-0.5709</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7179</v>
+        <v>-0.3135</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6088</v>
+        <v>-0.2574</v>
       </c>
       <c r="V15" t="n">
         <v>-2.0168</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0143</v>
+        <v>-0.4058</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0616</v>
+        <v>-1.6683</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0473</v>
+        <v>1.2625</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4902</v>
@@ -1702,13 +1702,13 @@
         <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0518</v>
+        <v>-0.3398</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5092</v>
+        <v>-0.0975</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4575</v>
+        <v>-0.2423</v>
       </c>
       <c r="V16" t="n">
         <v>0.6428</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.606</v>
+        <v>-0.4439</v>
       </c>
       <c r="E17" t="n">
         <v>-0.2736</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3324</v>
+        <v>-0.1703</v>
       </c>
       <c r="G17" t="n">
         <v>0.8934</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-0.6892</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3631</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4881</v>
+        <v>-0.3261</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4294</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2987</v>
+        <v>-0.9293</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8819</v>
+        <v>-1.3764</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5833</v>
+        <v>0.4471</v>
       </c>
       <c r="G18" t="n">
         <v>2.693</v>
@@ -1858,13 +1858,13 @@
         <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9548</v>
+        <v>-0.5854</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3494</v>
+        <v>0.1562</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6054</v>
+        <v>-0.7416</v>
       </c>
       <c r="V18" t="n">
         <v>-2.0601</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7959</v>
+        <v>-1.789</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2319</v>
+        <v>-0.0308</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5641</v>
+        <v>-1.7582</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0651</v>
+        <v>0.9966</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-0.6754</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.09470000000000001</v>
+        <v>1.6719</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1849</v>
+        <v>0.1975</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5513</v>
+        <v>-0.5308</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.7284</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1199</v>
+        <v>0.799</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.419</v>
+        <v>-0.1445</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5389</v>
+        <v>0.9435</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.586</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1448</v>
+        <v>-0.9891</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2888</v>
+        <v>-0.2283</v>
       </c>
       <c r="U19" t="n">
-        <v>0.144</v>
+        <v>-0.7608</v>
       </c>
       <c r="V19" t="n">
+        <v>-2.3824</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.2186</v>
-      </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-2.3824</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1144</v>
+        <v>-2.1306</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0308</v>
+        <v>-1.1307</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0836</v>
+        <v>-0.9998</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9966</v>
+        <v>-1.0651</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6754</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6719</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1975</v>
+        <v>-1.1849</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5308</v>
+        <v>-0.5513</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7284</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.799</v>
+        <v>0.1199</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1445</v>
+        <v>-0.419</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9435</v>
+        <v>0.5389</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.4795</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.1877</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.2918</v>
+      </c>
+      <c r="V20" t="n">
         <v>0</v>
       </c>
-      <c r="R20" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-1.3146</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-0.2283</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-1.0863</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-2.3824</v>
-      </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.3824</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0305</v>
+        <v>-3.6791</v>
       </c>
       <c r="E21" t="n">
         <v>-2.1714</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.859</v>
+        <v>-1.5077</v>
       </c>
       <c r="G21" t="n">
         <v>0.1164</v>
@@ -2092,13 +2092,13 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.5847</v>
       </c>
       <c r="T21" t="n">
         <v>-0.5364</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3997</v>
+        <v>-0.0483</v>
       </c>
       <c r="V21" t="n">
         <v>-2.0388</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2771</v>
+        <v>-3.8025</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1928</v>
+        <v>-1.9906</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0842</v>
+        <v>-1.8119</v>
       </c>
       <c r="G22" t="n">
         <v>0.1217</v>
@@ -2170,13 +2170,13 @@
         <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3207</v>
+        <v>-0.8461</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3494</v>
+        <v>-0.1471</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-0.6989</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4921</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.265699999999999</v>
+        <v>-7.9174</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.255599999999999</v>
+        <v>-4.255500000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.0098</v>
+        <v>-3.6617</v>
       </c>
       <c r="G23" t="n">
         <v>8.160200000000001</v>
@@ -2248,13 +2248,13 @@
         <v>13.674</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.4383</v>
+        <v>-5.090199999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3607</v>
+        <v>-1.3608</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.0777</v>
+        <v>-3.7294</v>
       </c>
       <c r="V23" t="n">
         <v>-11.9639</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484263_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484263_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9436</v>
+        <v>3.8515</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8808</v>
+        <v>2.7448</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0629</v>
+        <v>1.1068</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8629</v>
+        <v>0.3957</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2443</v>
+        <v>1.0954</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6186</v>
+        <v>-0.6998</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5903</v>
+        <v>1.1742</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3753</v>
+        <v>2.6823</v>
       </c>
       <c r="L2" t="n">
-        <v>1.215</v>
+        <v>-1.5081</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7273</v>
+        <v>-0.7785</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.131</v>
+        <v>-1.5868</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4037</v>
+        <v>0.8083</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.3441</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.2975</v>
+        <v>-3.3208</v>
       </c>
       <c r="R2" t="n">
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5812</v>
+        <v>1.0345</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5415</v>
+        <v>1.2355</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0398</v>
+        <v>-0.201</v>
       </c>
       <c r="V2" t="n">
-        <v>3.8436</v>
+        <v>3.7887</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0466</v>
+        <v>3.6559</v>
       </c>
       <c r="X2" t="n">
-        <v>0.797</v>
+        <v>0.1328</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +653,72 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8515</v>
+        <v>3.0227</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7448</v>
+        <v>1.9598</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1068</v>
+        <v>1.0629</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3957</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0954</v>
+        <v>-0.6766</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6998</v>
+        <v>1.6186</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1742</v>
+        <v>2.6693</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6823</v>
+        <v>1.4543</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.5081</v>
+        <v>1.215</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7785</v>
+        <v>-1.7273</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5868</v>
+        <v>-2.131</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8083</v>
+        <v>0.4037</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3674</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.3208</v>
+        <v>-4.2975</v>
       </c>
       <c r="R3" t="n">
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0345</v>
+        <v>0.5812</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2355</v>
+        <v>0.5415</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.201</v>
+        <v>0.0398</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7887</v>
+        <v>3.8436</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6559</v>
+        <v>3.0466</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1328</v>
+        <v>0.797</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2959</v>
+        <v>2.0072</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2203</v>
+        <v>0.3646</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0755</v>
+        <v>1.6427</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0719</v>
+        <v>1.2935</v>
       </c>
       <c r="H5" t="n">
-        <v>0.142</v>
+        <v>-0.5669</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9298999999999999</v>
+        <v>1.8604</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1664</v>
+        <v>2.3419</v>
       </c>
       <c r="K5" t="n">
-        <v>1.045</v>
+        <v>0.8851</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1214</v>
+        <v>1.4568</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0945</v>
+        <v>-1.0484</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.903</v>
+        <v>-1.452</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8085</v>
+        <v>0.4037</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.3441</v>
       </c>
       <c r="R5" t="n">
         <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6651</v>
+        <v>0.8934</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.3668</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1116</v>
+        <v>0.5266</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8086</v>
+        <v>0.797</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0858</v>
+        <v>0.797</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0072</v>
+        <v>1.9889</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3646</v>
+        <v>1.9133</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6427</v>
+        <v>0.0755</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2935</v>
+        <v>0.7649</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5669</v>
+        <v>-0.165</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8604</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3419</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8851</v>
+        <v>0.738</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4568</v>
+        <v>0.1214</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0484</v>
+        <v>-0.0945</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.452</v>
+        <v>-0.903</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4037</v>
+        <v>0.8085</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8934</v>
+        <v>0.6651</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3668</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5266</v>
+        <v>-0.1116</v>
       </c>
       <c r="V6" t="n">
-        <v>0.797</v>
+        <v>-0.8086</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>0.797</v>
+        <v>-1.0858</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4706</v>
+        <v>0.921</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9749</v>
+        <v>0.921</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4455</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5006</v>
+        <v>0.921</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.7266</v>
+        <v>0.921</v>
       </c>
       <c r="I7" t="n">
-        <v>2.226</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8105</v>
+        <v>0.921</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9584</v>
+        <v>0.921</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1478</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7682</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0782</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2373</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4067</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1694</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9059</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1328</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6389</v>
+        <v>0.4706</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8045</v>
+        <v>-0.9749</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1656</v>
+        <v>1.4455</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4752</v>
+        <v>-0.5006</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9762</v>
+        <v>-2.7266</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.499</v>
+        <v>2.226</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7117</v>
+        <v>-0.8105</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0781</v>
+        <v>-1.9584</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.1478</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7635999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8982</v>
+        <v>-0.7682</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1346</v>
+        <v>1.0782</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7814</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3441</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3323</v>
+        <v>0.2373</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.4067</v>
       </c>
       <c r="U8" t="n">
-        <v>0.425</v>
+        <v>-0.1694</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>1.9059</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0.1328</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.889</v>
+        <v>0.307</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.11</v>
+        <v>0.307</v>
       </c>
       <c r="F9" t="n">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1952</v>
+        <v>0.307</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.197</v>
+        <v>0.307</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9982</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2266</v>
+        <v>0.307</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6335</v>
+        <v>0.307</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9686</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5636</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7202</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5621</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1581</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1234,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1466</v>
+        <v>-0.6389</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5335</v>
+        <v>-0.8045</v>
       </c>
       <c r="F10" t="n">
-        <v>0.387</v>
+        <v>0.1656</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0024</v>
+        <v>-1.4752</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4088</v>
+        <v>-0.9762</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5936</v>
+        <v>-0.499</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.5131</v>
+        <v>-0.7117</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.92</v>
+        <v>-0.0781</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4893</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4889</v>
+        <v>-0.8982</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0004</v>
+        <v>0.1346</v>
       </c>
       <c r="P10" t="n">
         <v>0.7814</v>
@@ -1234,28 +1279,33 @@
         <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7972</v>
+        <v>0.3323</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7024</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0949</v>
+        <v>0.425</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2772</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5623</v>
+        <v>-0.889</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7785</v>
+        <v>-1.11</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2162</v>
+        <v>0.221</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4489</v>
+        <v>-3.1952</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2223</v>
+        <v>-2.197</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2266</v>
+        <v>-0.9982</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5455</v>
+        <v>-2.2266</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1845</v>
+        <v>-1.6335</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.361</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9034</v>
+        <v>-0.9686</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0379</v>
+        <v>-0.5636</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1344</v>
+        <v>-0.4051</v>
       </c>
       <c r="P11" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>0.855</v>
+        <v>0.7202</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7437</v>
+        <v>0.5621</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1113</v>
+        <v>0.1581</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5545</v>
+        <v>0.6093</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5545</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,224 +1400,235 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.1732</v>
+        <v>-1.1466</v>
       </c>
       <c r="E12" t="n">
-        <v>5.9179</v>
+        <v>-1.5335</v>
       </c>
       <c r="F12" t="n">
-        <v>4.255599999999999</v>
+        <v>0.387</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.16</v>
+        <v>-3.0024</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.510199999999999</v>
+        <v>-2.4088</v>
       </c>
       <c r="I12" t="n">
-        <v>1.350000000000001</v>
+        <v>-0.5936</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7978000000000005</v>
+        <v>-2.5131</v>
       </c>
       <c r="K12" t="n">
-        <v>1.217300000000001</v>
+        <v>-1.92</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0154</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.3622</v>
+        <v>-0.4893</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.7278</v>
+        <v>-0.4889</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3655</v>
+        <v>-0.0004</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.6739</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>12.6973</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>7.3461</v>
+        <v>0.7972</v>
       </c>
       <c r="T12" t="n">
-        <v>5.9856</v>
+        <v>0.7024</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3606</v>
+        <v>0.0949</v>
       </c>
       <c r="V12" t="n">
-        <v>11.9638</v>
+        <v>0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>14.4042</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4403</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FRIVALCA LA MUELA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.286</v>
+        <v>-2.5623</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1672</v>
+        <v>-2.7785</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1188</v>
+        <v>0.2162</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-3.4489</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1397</v>
+        <v>-2.2223</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9043</v>
+        <v>-1.2266</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2602</v>
+        <v>-2.5455</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3735</v>
+        <v>-1.1845</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.361</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5044</v>
+        <v>-0.9034</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2338</v>
+        <v>-1.0379</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2706</v>
+        <v>0.1344</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2009</v>
+        <v>0.855</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3537</v>
+        <v>0.7437</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1529</v>
+        <v>0.1113</v>
       </c>
       <c r="V13" t="n">
-        <v>1.873</v>
+        <v>-0.5545</v>
       </c>
       <c r="W13" t="n">
-        <v>2.0503</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1773</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FRIVALCA LA MUELA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9086</v>
+        <v>10.1733</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0511</v>
+        <v>5.9179</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1425</v>
+        <v>4.255599999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5658</v>
+        <v>-8.1599</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2566</v>
+        <v>-9.5101</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3091</v>
+        <v>1.350000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6657</v>
+        <v>-0.7977999999999987</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6253</v>
+        <v>1.2173</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0405</v>
+        <v>-2.0154</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1</v>
+        <v>-7.362200000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3686</v>
+        <v>-10.7278</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2687</v>
+        <v>3.365499999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>-0.9766999999999996</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-13.6739</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>12.6973</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2064</v>
+        <v>7.3461</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0029</v>
+        <v>5.9856</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2093</v>
+        <v>1.3606</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.0601</v>
+        <v>11.9638</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6642</v>
+        <v>14.4042</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3959</v>
-      </c>
+        <v>-2.4403</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0682</v>
+        <v>2.4489</v>
       </c>
       <c r="E15" t="n">
-        <v>1.168</v>
+        <v>2.4489</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0997</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0932</v>
+        <v>2.4489</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4979</v>
+        <v>1.8419</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4047</v>
+        <v>0.607</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4581</v>
+        <v>2.4489</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4572</v>
+        <v>1.8419</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001</v>
+        <v>0.607</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3649</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4056</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5709</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3135</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2574</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.0168</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.0168</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4058</v>
+        <v>2.286</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6683</v>
+        <v>1.1672</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2625</v>
+        <v>1.1188</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.4902</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0593</v>
+        <v>0.1397</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5495</v>
+        <v>-0.9043</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7812</v>
+        <v>-0.2602</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7674</v>
+        <v>0.3735</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.5486</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7091</v>
+        <v>-0.5044</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7081</v>
+        <v>-0.2338</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.001</v>
+        <v>-0.2706</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7348</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3398</v>
+        <v>0.2009</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0975</v>
+        <v>0.3537</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2423</v>
+        <v>-0.1529</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6428</v>
+        <v>1.873</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1638</v>
+        <v>2.0503</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.521</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4439</v>
+        <v>1.9086</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2736</v>
+        <v>2.0511</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1703</v>
+        <v>-0.1425</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8934</v>
+        <v>4.5658</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7716</v>
+        <v>4.2566</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1218</v>
+        <v>0.3091</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0895</v>
+        <v>4.6657</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1023</v>
+        <v>4.6253</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0128</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8038999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6692</v>
+        <v>-0.3686</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1346</v>
+        <v>0.2687</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6892</v>
+        <v>-0.2064</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3631</v>
+        <v>0.0029</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3261</v>
+        <v>-0.2093</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4294</v>
+        <v>-2.0601</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4294</v>
+        <v>-1.3959</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9293</v>
+        <v>-0.4058</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3764</v>
+        <v>-1.6683</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4471</v>
+        <v>1.2625</v>
       </c>
       <c r="G18" t="n">
-        <v>2.693</v>
+        <v>-1.4902</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3988</v>
+        <v>0.0593</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2941</v>
+        <v>-1.5495</v>
       </c>
       <c r="J18" t="n">
-        <v>1.085</v>
+        <v>-0.7812</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0041</v>
+        <v>0.7674</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>-1.5486</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6079</v>
+        <v>-0.7091</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3948</v>
+        <v>-0.7081</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2132</v>
+        <v>-0.001</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>2.7348</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5854</v>
+        <v>-0.3398</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1562</v>
+        <v>-0.0975</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7416</v>
+        <v>-0.2423</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.0601</v>
+        <v>0.6428</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>1.1638</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3959</v>
+        <v>-0.521</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.789</v>
+        <v>-0.4439</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0308</v>
+        <v>-0.2736</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7582</v>
+        <v>-0.1703</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9966</v>
+        <v>0.8934</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6754</v>
+        <v>0.7716</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6719</v>
+        <v>0.1218</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1975</v>
+        <v>0.0895</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5308</v>
+        <v>0.1023</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7284</v>
+        <v>-0.0128</v>
       </c>
       <c r="M19" t="n">
-        <v>0.799</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1445</v>
+        <v>0.6692</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9435</v>
+        <v>0.1346</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9891</v>
+        <v>-0.6892</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2283</v>
+        <v>-0.3631</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7608</v>
+        <v>-0.3261</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.3824</v>
+        <v>-1.4294</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3824</v>
+        <v>-1.4294</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1306</v>
+        <v>-0.9293</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1307</v>
+        <v>-1.3764</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9998</v>
+        <v>0.4471</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0651</v>
+        <v>2.693</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9703000000000001</v>
+        <v>1.3988</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.09470000000000001</v>
+        <v>1.2941</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1849</v>
+        <v>1.085</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5513</v>
+        <v>1.0041</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1199</v>
+        <v>1.6079</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.419</v>
+        <v>0.3948</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5389</v>
+        <v>1.2132</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4795</v>
+        <v>-0.5854</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1877</v>
+        <v>0.1562</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2918</v>
+        <v>-0.7416</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.0601</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-1.3959</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6791</v>
+        <v>-1.3807</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1714</v>
+        <v>-1.2809</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5077</v>
+        <v>-0.0997</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1164</v>
+        <v>-0.3557</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6805</v>
+        <v>0.6559</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5641</v>
+        <v>-1.0116</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2951</v>
+        <v>0.0092</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0491</v>
+        <v>0.6152</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.754</v>
+        <v>-0.606</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1787</v>
+        <v>-0.3649</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3686</v>
+        <v>0.0407</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8101</v>
+        <v>-0.4056</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5847</v>
+        <v>-0.5709</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5364</v>
+        <v>-0.3135</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0483</v>
+        <v>-0.2574</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0388</v>
+        <v>-2.0168</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0388</v>
+        <v>-2.0168</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8025</v>
+        <v>-1.789</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9906</v>
+        <v>-0.0308</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8119</v>
+        <v>-1.7582</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1217</v>
+        <v>0.9966</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3515</v>
+        <v>-0.6754</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2298</v>
+        <v>1.6719</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2026</v>
+        <v>0.1975</v>
       </c>
       <c r="K22" t="n">
-        <v>0.431</v>
+        <v>-0.5308</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.7284</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3243</v>
+        <v>0.799</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0795</v>
+        <v>-0.1445</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4039</v>
+        <v>0.9435</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.586</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8461</v>
+        <v>-0.9891</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1471</v>
+        <v>-0.2283</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6989</v>
+        <v>-0.7608</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4921</v>
+        <v>-2.3824</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8279</v>
+        <v>-2.3824</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,318 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9174</v>
+        <v>-2.1306</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.255500000000001</v>
+        <v>-1.1307</v>
       </c>
       <c r="F23" t="n">
+        <v>-0.9998</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.0651</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.9703000000000001</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.09470000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.1849</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.5513</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.419</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.4795</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.1877</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.2918</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M. CASADO FAJO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-3.6791</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2.1714</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.5077</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1164</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.6805</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.5641</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.2951</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.0491</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.754</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.1787</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.3686</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.8101</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.5847</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.5364</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-2.0388</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.0388</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L. PERALTA VISTUE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.8025</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.9906</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.8119</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.2298</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.2026</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.0795</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.8461</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.1471</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.6989</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-2.4921</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484263_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-7.917399999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.2555</v>
+      </c>
+      <c r="F26" t="n">
         <v>-3.6617</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G26" t="n">
         <v>8.160200000000001</v>
       </c>
-      <c r="H23" t="n">
-        <v>9.510199999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-1.3502</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="H26" t="n">
+        <v>9.5101</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.3501</v>
+      </c>
+      <c r="J26" t="n">
         <v>7.361999999999999</v>
       </c>
-      <c r="K23" t="n">
-        <v>10.7278</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K26" t="n">
+        <v>10.7277</v>
+      </c>
+      <c r="L26" t="n">
         <v>-3.3654</v>
       </c>
-      <c r="M23" t="n">
-        <v>0.7979000000000003</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="M26" t="n">
+        <v>0.7978999999999998</v>
+      </c>
+      <c r="N26" t="n">
         <v>-1.2174</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O26" t="n">
         <v>2.0155</v>
       </c>
-      <c r="P23" t="n">
-        <v>0.9767000000000005</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="P26" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q26" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>13.674</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S26" t="n">
         <v>-5.090199999999999</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>-1.3608</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>-3.7294</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>-11.9639</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W26" t="n">
         <v>2.4401</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>-14.404</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
